--- a/Module2-WasteManagementanalyticsbyakshit.xlsx
+++ b/Module2-WasteManagementanalyticsbyakshit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akshi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53A9E66C-8C46-4FA7-A030-CF91E4785DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22DF80A6-5278-4CF3-9781-834D07864910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="68">
   <si>
     <t>Timestamp</t>
   </si>
@@ -277,6 +277,9 @@
   <si>
     <t>MOST TYPE OF WASTE GENERATED</t>
   </si>
+  <si>
+    <t>Count of Waste_Amount_kg</t>
+  </si>
 </sst>
 </file>
 
@@ -356,7 +359,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -390,6 +393,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -569,10 +578,11 @@
       </font>
       <fill>
         <patternFill>
+          <fgColor theme="2" tint="-0.24994659260841701"/>
           <bgColor theme="1" tint="0.24994659260841701"/>
         </patternFill>
       </fill>
-      <border>
+      <border diagonalDown="1">
         <left style="thin">
           <color theme="0" tint="-0.499984740745262"/>
         </left>
@@ -585,6 +595,9 @@
         <bottom style="thin">
           <color theme="0" tint="-0.499984740745262"/>
         </bottom>
+        <diagonal style="thin">
+          <color theme="0" tint="-0.499984740745262"/>
+        </diagonal>
         <vertical/>
         <horizontal/>
       </border>
@@ -2672,13 +2685,13 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>14974</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20606</c:v>
+                  <c:v>81</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>17693</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3562,7 +3575,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="2400"/>
-              <a:t>COLLECTION STATUS BY LOCATION</a:t>
+              <a:t>TOTAL COLLECTION BY LOCATION</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8087,13 +8100,13 @@
       <xdr:col>38</xdr:col>
       <xdr:colOff>532</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>168674</xdr:rowOff>
+      <xdr:rowOff>79027</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
       <xdr:colOff>12290</xdr:colOff>
       <xdr:row>65</xdr:row>
-      <xdr:rowOff>45902</xdr:rowOff>
+      <xdr:rowOff>74705</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -8129,8 +8142,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="23571732" y="6129207"/>
-              <a:ext cx="2450158" cy="6024028"/>
+              <a:off x="23592052" y="6098827"/>
+              <a:ext cx="2450158" cy="6030718"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8163,15 +8176,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>1049</xdr:rowOff>
+      <xdr:colOff>4211</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>162350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>654</xdr:colOff>
+      <xdr:colOff>4864</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>165253</xdr:rowOff>
+      <xdr:rowOff>147260</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -8207,8 +8220,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="23571201" y="2795049"/>
-              <a:ext cx="2439053" cy="1654337"/>
+              <a:off x="23595731" y="2890310"/>
+              <a:ext cx="2439053" cy="1630830"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8240,16 +8253,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>819</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>569636</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>150547</xdr:rowOff>
+      <xdr:rowOff>108039</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>42</xdr:col>
-      <xdr:colOff>12290</xdr:colOff>
+      <xdr:colOff>6924</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>147761</xdr:rowOff>
+      <xdr:rowOff>105253</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
       <mc:Choice Requires="a14">
@@ -8285,8 +8298,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="23572019" y="4620947"/>
-              <a:ext cx="2449871" cy="1301081"/>
+              <a:off x="23582036" y="4664799"/>
+              <a:ext cx="2454808" cy="1277374"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -8361,7 +8374,7 @@
                 <a:schemeClr val="bg1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>TIMES</a:t>
+            <a:t>TIME</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-IN" sz="2000" b="1" kern="1200" baseline="0">
@@ -10886,296 +10899,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A118EAE-B0AC-4634-A677-26F3D827C20F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="7"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="21">
-        <item x="5"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="16"/>
-        <item x="9"/>
-        <item x="19"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Waste_Type" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="5">
-    <chartFormat chart="5" format="10" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="12">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="13">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="14">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="5" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C72F571-74D4-4256-A433-C4898F5FFFDA}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
-  <location ref="L1:M7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="10">
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="9">
-        <item x="7"/>
-        <item x="4"/>
-        <item x="6"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0">
-      <items count="21">
-        <item x="5"/>
-        <item x="14"/>
-        <item x="7"/>
-        <item x="13"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="12"/>
-        <item x="18"/>
-        <item x="11"/>
-        <item x="1"/>
-        <item x="10"/>
-        <item x="16"/>
-        <item x="9"/>
-        <item x="19"/>
-        <item x="8"/>
-        <item x="15"/>
-        <item x="2"/>
-        <item x="17"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="2"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Truck_ID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5918FF7D-AEDF-4413-892B-463B32823144}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="J1:K34" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -11375,7 +11098,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4A036ED9-01D8-4BDC-8F85-E270A3FF2D32}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="H4:I25" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -11538,7 +11261,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B15E4AE4-69E5-4A6B-97B4-3FF57025B55C}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="E1:F5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -11625,7 +11348,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of Waste_Amount_kg" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Count of Waste_Amount_kg" fld="6" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="5" format="2" series="1">
@@ -11650,7 +11373,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{94D6F431-6C99-460E-A256-BAAC9A4853E7}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="C1:D22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
@@ -11789,6 +11512,296 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Sum of Waste_Amount_kg" fld="6" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A118EAE-B0AC-4634-A677-26F3D827C20F}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+  <location ref="A1:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="7"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="21">
+        <item x="5"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="9"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Waste_Type" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="5" format="10" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="12">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="5" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7C72F571-74D4-4256-A433-C4898F5FFFDA}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="L1:M7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="10">
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="9">
+        <item x="7"/>
+        <item x="4"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0">
+      <items count="21">
+        <item x="5"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="13"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="12"/>
+        <item x="18"/>
+        <item x="11"/>
+        <item x="1"/>
+        <item x="10"/>
+        <item x="16"/>
+        <item x="9"/>
+        <item x="19"/>
+        <item x="8"/>
+        <item x="15"/>
+        <item x="2"/>
+        <item x="17"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Truck_ID" fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="5" format="2" series="1">
@@ -18718,7 +18731,7 @@
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.5546875" bestFit="1" customWidth="1"/>
@@ -18744,7 +18757,7 @@
         <v>55</v>
       </c>
       <c r="F1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>55</v>
@@ -18776,7 +18789,7 @@
         <v>29</v>
       </c>
       <c r="F2">
-        <v>14974</v>
+        <v>52</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>51</v>
@@ -18808,7 +18821,7 @@
         <v>15</v>
       </c>
       <c r="F3">
-        <v>20606</v>
+        <v>81</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>29</v>
@@ -18840,7 +18853,7 @@
         <v>21</v>
       </c>
       <c r="F4">
-        <v>17693</v>
+        <v>67</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>55</v>
@@ -18878,7 +18891,7 @@
         <v>56</v>
       </c>
       <c r="F5">
-        <v>53273</v>
+        <v>200</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>36</v>
